--- a/data/trans_orig/IP16B06-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16B06-Edad-trans_orig.xlsx
@@ -3778,7 +3778,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,02%</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
